--- a/reports/informe_eudr_tablas.xlsx
+++ b/reports/informe_eudr_tablas.xlsx
@@ -19,17 +19,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_indice_preparacion_EUDR" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_8_vigencia_mandatos" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_reconciliacion_peso" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_origen_incoherente" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_fechas_invertidas" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_01_identificacion" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_02_perfil_agronomico" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_03_certificaciones" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_04_intervencion_pac" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_05_beneficiarios_historic" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_06_asistencia_tecnica" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_07_ventas_historicas" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_08_comprobantes_2025" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_09_estado_sunat" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_IP_insumos_PPA_SUNAT_sanitario" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_IV1_dependencia_UE" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_capa_confianza_triangulacion" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_mapa_cobertura_IP_IV" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_origen_incoherente" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_fechas_invertidas" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_01_identificacion" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_02_perfil_agronomico" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_03_certificaciones" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_04_intervencion_pac" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_05_beneficiarios_historic" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_06_asistencia_tecnica" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_07_ventas_historicas" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_08_comprobantes_2025" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anexo_09_estado_sunat" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4549,529 +4553,559 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ruc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>organizacion</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>region_real</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>origen_declarado</t>
+          <t>ppa_registrado_ip1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>coherente</t>
+          <t>sunat_formal_ip2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>registro_sanitario_ip4</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>20132489824</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>san martin</t>
-        </is>
+      <c r="C2" t="b">
+        <v>1</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sin registro</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>20132505455</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C3" t="b">
+        <v>1</v>
       </c>
       <c r="D3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>20132517119</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C4" t="b">
+        <v>1</v>
       </c>
       <c r="D4" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sin registro</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>20136201213</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C5" t="b">
+        <v>1</v>
       </c>
       <c r="D5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>20140181405</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera la Florida</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Junín</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>san martin</t>
-        </is>
+      <c r="C6" t="b">
+        <v>1</v>
       </c>
       <c r="D6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>20140292657</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C7" t="b">
+        <v>1</v>
       </c>
       <c r="D7" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sin registro</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>20147443120</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>san martin</t>
-        </is>
+      <c r="C8" t="b">
+        <v>1</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sin registro</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>20200880448</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>san martin</t>
-        </is>
+      <c r="C9" t="b">
+        <v>1</v>
       </c>
       <c r="D9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sin registro</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>20479595276</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera CASIL LTDA</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Cajamarca</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C10" t="b">
+        <v>1</v>
       </c>
       <c r="D10" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>20542209951</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Valle Grande</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C11" t="b">
+        <v>1</v>
       </c>
       <c r="D11" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sin registro</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>20542264544</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Valle del Biavo Ltda</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C12" t="b">
+        <v>1</v>
       </c>
       <c r="D12" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>20561140091</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C13" t="b">
+        <v>1</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>20600263286</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C14" t="b">
+        <v>1</v>
       </c>
       <c r="D14" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>20609846314</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C15" t="b">
+        <v>1</v>
       </c>
       <c r="D15" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>20600920597</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Yuraq Yacu</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ayacucho</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>san martin</t>
-        </is>
+      <c r="C16" t="b">
+        <v>1</v>
       </c>
       <c r="D16" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>20601558204</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera OCUMAL</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C17" t="b">
+        <v>1</v>
       </c>
       <c r="D17" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>20602054480</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Pasco</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C18" t="b">
+        <v>1</v>
       </c>
       <c r="D18" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>20602488927</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Junín</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C19" t="b">
+        <v>1</v>
       </c>
       <c r="D19" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>20602650643</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Asociación Agroexportadora de la Región San Martín</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C20" t="b">
+        <v>1</v>
       </c>
       <c r="D20" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sin registro</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>20603820691</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C21" t="b">
+        <v>1</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>20603862369</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Cooperativa Agria Tropical Products</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Junín</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C22" t="b">
+        <v>1</v>
       </c>
       <c r="D22" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" t="n">
+        <v>20604309728</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cajamarca</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C23" t="b">
+        <v>1</v>
       </c>
       <c r="D23" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="n">
+        <v>20605500430</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Junín</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C24" t="b">
+        <v>1</v>
       </c>
       <c r="D24" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" t="n">
+        <v>20606451122</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Asociación de Productores Cerro Blanco</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>pacMAYOR|san martin</t>
-        </is>
+      <c r="C25" t="b">
+        <v>1</v>
       </c>
       <c r="D25" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" t="n">
+        <v>20610286519</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Line Coffee Marañon</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>san martin</t>
-        </is>
+      <c r="C26" t="b">
+        <v>1</v>
       </c>
       <c r="D26" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5085,125 +5119,347 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ruc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>organizacion</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>inicio_actividades</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>inscripcion_sunat</t>
+          <t>fob_ue</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>fecha_invertida</t>
+          <t>fob_no_ue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fob_total</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pct_fob_ue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>20542209951</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Valle Grande</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7878141.732</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3843266.891</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11721408.623</v>
+      </c>
+      <c r="F2" t="n">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>20602650643</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Asociación Agroexportadora de la Región San Martín</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4575551.37</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2111310.138</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6686861.508</v>
+      </c>
+      <c r="F3" t="n">
+        <v>68.40000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>20479595276</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera CASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>965167.446</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3503411.512</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4468578.958000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>20136201213</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>894391.265</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3521220.478</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4415611.743</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>20140181405</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera la Florida</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>644581.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3540140.93</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4184722.23</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>20600263286</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2059443.824</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2095124.002</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4154567.826</v>
+      </c>
+      <c r="F7" t="n">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>20603820691</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>852880.4399999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>348246.12</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1201126.56</v>
+      </c>
+      <c r="F8" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>20542264544</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Valle del Biavo Ltda</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>41626</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>41261</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>42095</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>42094</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>44873</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>44784</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Yuraq Yacu</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>42416</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>42376</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C9" t="n">
+        <v>1187600.476</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1187600.476</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>20606451122</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Cerro Blanco</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>76135.47</v>
+      </c>
+      <c r="D10" t="n">
+        <v>864647.85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>940783.3199999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>20602054480</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>813479.675</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>813479.675</v>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>20601558204</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera OCUMAL</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>442439.35</v>
+      </c>
+      <c r="E12" t="n">
+        <v>442439.35</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>20603862369</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Cooperativa Agria Tropical Products</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>43435</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>43433</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Line Coffee Marañon</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>44986</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>44889</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
+      <c r="C13" t="n">
+        <v>332555.16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>332555.16</v>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>20605500430</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>147669.481</v>
+      </c>
+      <c r="E14" t="n">
+        <v>147669.481</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20604309728</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7275.18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7275.18</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5223,272 +5479,240 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>ruc</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Organización</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Región</t>
+          <t>fiabilidad_autorreporte</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Provincia</t>
+          <t>organica_declarada_coincide_aduana</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Contribuyente (SUNAT)</t>
+          <t>fairtrade_declarado_coincide_aduana</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CIIU Principal</t>
+          <t>nivel_confianza_triangulacion</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20132489824</v>
+        <v>20542209951</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
+          <t>Cooperativa Agraria Valle Grande</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Calca</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Diverge +6%</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRANSPORTE DE CARGA POR CARRETERA.</t>
+          <t>Baja (diverge en todo lo verificable)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20132505455</v>
+        <v>20602650643</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
+          <t>Asociación Agroexportadora de la Región San Martín</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>La Convención</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Diverge +2%</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>EXPLOTACION MIXTA.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20132517119</v>
+        <v>20600263286</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
+          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>La Convención</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Coincide con Aduanas</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ELAB. CACAO, CHOCOLATE Y CONFIT.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20136201213</v>
+        <v>20140181405</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
+          <t>Cooperativa Agraria Cafetalera la Florida</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>La Convención</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Coincide con Aduanas</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VTA. MAY. DE OTROS PRODUCTOS.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20140181405</v>
+        <v>20136201213</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera la Florida</t>
+          <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Junín</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Chanchamayo</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Diverge -9%</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CULTIVO DE FRUTAS.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20140292657</v>
+        <v>20542264544</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
+          <t>Cooperativa Agraria Valle del Biavo Ltda</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>La Convención</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Coincide con Aduanas</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CULTIVO DE FRUTAS.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20147443120</v>
+        <v>20603862369</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
+          <t>Cooperativa Agria Tropical Products</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>La Convención</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Coincide con Aduanas</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VTA. MAY. MATERIALES DE CONSTRUCCION.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20200880448</v>
+        <v>20605500430</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
+          <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cusco</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Calca</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Coincide con Aduanas</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VTA. MAY. DE OTROS PRODUCTOS.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
@@ -5503,472 +5727,368 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cajamarca</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>San Ignacio</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Diverge -12%</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CULTIVOS DE CEREALES.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20542209951</v>
+        <v>20606451122</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Valle Grande</t>
+          <t>Asociación de Productores Cerro Blanco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Moyobamba</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Coincide con Aduanas</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VTA. MIN. ALIMENTOS, BEBIDAS, TABACO.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20542264544</v>
+        <v>20602054480</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Valle del Biavo Ltda</t>
+          <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bellavista</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Diverge -10%</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CULTIVOS DE CEREALES.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20561140091</v>
+        <v>20603820691</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
+          <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Utcubamba</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Diverge +24%</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CULTIVOS DE CEREALES.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20600263286</v>
+        <v>20604309728</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
+          <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Moyobamba</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ASOCIACION</t>
-        </is>
+          <t>Coincide con Aduanas</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VTA. MAY. DE MATERIAS PRIMAS AGROPEC.</t>
+          <t>Media (coincide parcialmente)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20609846314</v>
+        <v>20132489824</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
+          <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Lamas</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CULTIVOS DE CEREALES.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20600920597</v>
+        <v>20132505455</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Yuraq Yacu</t>
+          <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ayacucho</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>La Mar</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VTA. MAY. ALIMENTOS, BEBIDAS Y TABACO.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20601558204</v>
+        <v>20132517119</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera OCUMAL</t>
+          <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Luya</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EXPLOTACION MIXTA.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20602054480</v>
+        <v>20140292657</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
+          <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pasco</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Oxapampa</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CULTIVO DE FRUTAS.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20602488927</v>
+        <v>20147443120</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
+          <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Junín</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Satipo</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VTA. MAY. DE MATERIAS PRIMAS AGROPEC.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20602650643</v>
+        <v>20200880448</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Asociación Agroexportadora de la Región San Martín</t>
+          <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Moyobamba</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ASOCIACION</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SERVICIOS AGRICOLAS, GANADERAS.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20603820691</v>
+        <v>20561140091</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
+          <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bellavista</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VTA. MAY. DE MATERIAS PRIMAS AGROPEC.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20603862369</v>
+        <v>20609846314</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cooperativa Agria Tropical Products</t>
+          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Junín</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Chanchamayo</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CULTIVOS DE CEREALES.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20604309728</v>
+        <v>20600920597</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
+          <t>Cooperativa Agraria Yuraq Yacu</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cajamarca</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>San Ignacio</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ASOCIACION</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CULTIVOS DE CEREALES.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20605500430</v>
+        <v>20601558204</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
+          <t>Cooperativa Agraria Cafetalera OCUMAL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Junín</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Chanchamayo</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
+          <t>Actividad exportadora detectada en Aduanas (US$ 442,439)</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CULTIVOS DE CEREALES.</t>
+          <t>Baja (diverge en todo lo verificable)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20606451122</v>
+        <v>20602488927</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Asociación de Productores Cerro Blanco</t>
+          <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Martín</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Moyobamba</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ASOCIACION</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VTA. MAY. DE MATERIAS PRIMAS AGROPEC.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
@@ -5983,22 +6103,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Utcubamba</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>COOPERATIVAS, SAIS, CAPS</t>
-        </is>
-      </c>
+          <t>Sin verificación externa (sin registro DUA)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CULTIVO DE FRUTAS.</t>
+          <t>Sin verificación externa (sin registro DUA)</t>
         </is>
       </c>
     </row>
@@ -6013,688 +6125,303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Organización</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Altitud de las unidades productivas: (rango - m.s.n.m)</t>
+          <t>subdimension</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de socios (varones)</t>
+          <t>cobertura_hoy</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Numero de socias (Mujeres)</t>
+          <t>fuente_externa_disponible</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Numero de hectareas totales de la organización</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Producto Dom</t>
+          <t>pendiente_de_instrumento_2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
+          <t>IP1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1400 - 2150 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
+          <t>Trazabilidad y origen</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PPA (inscripción organizacional, Art. 9); ítem lote/ICO en Aduanas (trazabilidad comercial, no de parcela)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Verificación a nivel de parcela/socio individual — solo vía Instrumento 2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
+          <t>IP2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1500 - 1950 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>73</v>
-      </c>
-      <c r="D3" t="n">
-        <v>27</v>
-      </c>
-      <c r="E3" t="n">
-        <v>218</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
+          <t>Cumplimiento ambiental/legal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fuerte (solo componente tributario)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estado y condición del contribuyente ante SUNAT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Evidencia de título de tierra y normativa ambiental de fondo — ninguna fuente administrativa disponible la cubre</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
+          <t>IP3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1400 - 2100 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>133</v>
-      </c>
-      <c r="D4" t="n">
-        <v>44</v>
-      </c>
-      <c r="E4" t="n">
-        <v>469</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
+          <t>Capacidades organizacionales</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Asistencias técnicas y talleres MIDAGRI 2020–2025; etapa del PAC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Política formal de debida diligencia (D5) y percepción de fricción/costos (D8) — solo Instrumento 2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
+          <t>IP4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1750 - 2200 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>472</v>
-      </c>
-      <c r="D5" t="n">
-        <v>188</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1670</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
+          <t>Información y documentación</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Parcial, reforzada en esta ronda</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Registro Sanitario y su vencimiento; antigüedad de mandato OECE (bandera, no se promedia)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Resto del expediente documental EUDR (DDS, mapas, contratos de abastecimiento) — solo Instrumento 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera la Florida</t>
+          <t>IP5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mayor a 1200 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>339</v>
-      </c>
-      <c r="D6" t="n">
-        <v>111</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1605.8</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
+          <t>Adaptación y acceso a recursos</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Financiamiento, costos de cumplimiento, acceso a crédito — íntegramente Instrumento 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
+          <t>IV1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1750 - 2200 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>38</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E7" t="n">
-        <v>136.9</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
+          <t>Dependencia del mercado europeo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fuerte, solo para 14 de 25 organizaciones</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ratio FOB UE / FOB total calculado directamente de Aduanas (pais_codigo por DUA)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Las 11 organizaciones sin registro DUA siguen dependiendo de la pregunta P1b de Instrumento 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
+          <t>IV2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1400 - 2100 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>44</v>
-      </c>
-      <c r="D8" t="n">
-        <v>30</v>
-      </c>
-      <c r="E8" t="n">
-        <v>150</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
+          <t>Exposición regulatoria</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ninguna en estas 3 fuentes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ya resuelta en el diseño con D1 completo — pendiente de aplicar Instrumento 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
+          <t>IV3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1600 - 2200 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>29</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" t="n">
-        <v>38</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
+          <t>Fragilidad productiva y territorial</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Muy parcial (proxy grueso de organización, no de socio)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hectáreas por socio y rango altitudinal declarados a nivel de organización</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dispersión geográfica real de los socios — gap ya identificado, pendiente de encuesta</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera CASIL LTDA</t>
+          <t>IV4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Café de altura</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>136</v>
-      </c>
-      <c r="D10" t="n">
-        <v>42</v>
-      </c>
-      <c r="E10" t="n">
-        <v>437</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
+          <t>Brechas tecnológicas y financieras</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Conectividad (D6.24) y costo de cumplimiento (D9) — íntegramente Instrumento 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Valle Grande</t>
+          <t>IV5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>800 - 2000 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>468</v>
-      </c>
-      <c r="D11" t="n">
-        <v>154</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4031</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Valle del Biavo Ltda</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1000 - 1500 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>372</v>
-      </c>
-      <c r="D12" t="n">
-        <v>44</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1200 - 2100 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>278</v>
-      </c>
-      <c r="D13" t="n">
-        <v>73</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1045.6</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>800 - 1600 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>607</v>
-      </c>
-      <c r="D14" t="n">
-        <v>190</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2110</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1000 - 1400 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>444</v>
-      </c>
-      <c r="D15" t="n">
-        <v>254</v>
-      </c>
-      <c r="E15" t="n">
-        <v>921.1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Yuraq Yacu</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>750 - 2000 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>75</v>
-      </c>
-      <c r="D16" t="n">
-        <v>19</v>
-      </c>
-      <c r="E16" t="n">
-        <v>94</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CACAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Cafetalera OCUMAL</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1300 - 2200 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>205</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
-      </c>
-      <c r="E17" t="n">
-        <v>685</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1100 - 1850 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>91</v>
-      </c>
-      <c r="D18" t="n">
-        <v>86</v>
-      </c>
-      <c r="E18" t="n">
-        <v>213</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1200 - 1500 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>103</v>
-      </c>
-      <c r="D19" t="n">
-        <v>59</v>
-      </c>
-      <c r="E19" t="n">
-        <v>454.5</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Asociación Agroexportadora de la Región San Martín</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1100 - 1700 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>607</v>
-      </c>
-      <c r="D20" t="n">
-        <v>155</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1000 - 1500 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>291</v>
-      </c>
-      <c r="D21" t="n">
-        <v>90</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1143</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Cooperativa Agria Tropical Products</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Mayor a 1200 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>135</v>
-      </c>
-      <c r="D22" t="n">
-        <v>68</v>
-      </c>
-      <c r="E22" t="n">
-        <v>609</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Café de altura</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>236</v>
-      </c>
-      <c r="D23" t="n">
-        <v>69</v>
-      </c>
-      <c r="E23" t="n">
-        <v>699</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Mayor a 1200 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>165</v>
-      </c>
-      <c r="D24" t="n">
-        <v>92</v>
-      </c>
-      <c r="E24" t="n">
-        <v>771</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Asociación de Productores Cerro Blanco</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>800 - 2000 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>141</v>
-      </c>
-      <c r="D25" t="n">
-        <v>46</v>
-      </c>
-      <c r="E25" t="n">
-        <v>600</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>CAFÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Line Coffee Marañon</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1100 - 2200 m s. n. m.</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>78</v>
-      </c>
-      <c r="D26" t="n">
-        <v>66</v>
-      </c>
-      <c r="E26" t="n">
-        <v>342.25</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>CAFE</t>
+          <t>Riesgo social y comercial</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Señal nueva, sin subdimensión asignada todavía</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Concentración en un mismo agente de aduana (10 de 13 exportadoras)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pendiente de decisión de alcance explícita (mismo criterio ya aplicado a CLPI en Instrumento 7) antes de incorporarla</t>
         </is>
       </c>
     </row>
@@ -6715,22 +6442,22 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Organización</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Certificación Organica vigente (colocar el numero de certificado y la fecha de la vigencia)</t>
+          <t>region_real</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Certificación Comercio Justo (colocar el numero de certificado y la fecha de la vigencia)</t>
+          <t>origen_declarado</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Con que otras certificaciones vigentes cuentan (tambien incluir la vigencia de cada uno)</t>
+          <t>coherente</t>
         </is>
       </c>
     </row>
@@ -6742,15 +6469,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Certificacion Organica, vigencia hasta 14/08/2026</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vigencia organica hasta 26/03/2027</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>san martin</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6760,11 +6489,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Certificacion Organica, 26 de noviembre del 2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6774,15 +6509,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Certificación Orgánica, Vigencia  hasta agosto 2026</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fairtrade hasta junio 2026</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6792,15 +6529,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Certificación Orgánica, vigencia hasta agosto 2026</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fair trade hasta junio 2027</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6810,18 +6549,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1780867353, VIGENCIA HASTA 06 FEB 2028</t>
+          <t>Junín</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FLO ID 796, VIGENCIA HASTA 24 DIC 2028</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>BIRD FRIENDEY y Fairtrade</t>
-        </is>
+          <t>san martin</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6832,16 +6569,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Certificacion Organica, , vigencia  hasta agosto 2026.</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-FairTrade (en proceso)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6851,15 +6589,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Certificacion Organica, vigencia hasta 14/08/2026</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vigencia organica hasta 26/03/2027</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>san martin</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6869,15 +6609,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Certificacion Organica, vigencia hasta 14/08/2026</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vigencia organica hasta 26/03/2027</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>san martin</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6887,15 +6629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Cajamarca</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6905,18 +6649,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si (CU827371 - Vence 24/08/2026) </t>
+          <t>San Martín</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Si ( FAIR TRADE INTERNACIONAL - 28953 - 27/07/2027), (FAIR TRADING USA - 101034770 - 27/07/2027)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>RAIN FOREST ( RA_00079662202, VENCE 24/08/2026)</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6927,19 +6669,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PE-BIO-149.604-0001347.2025.002 VIGENCIA 07/09/2026</t>
+          <t>San Martín</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FLO ID: 30733  vigencia (02/02/2028)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rainforest Alliance  RA_00079682202 vigencia(15/07/2027) C831412RA_01_2025
-</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6950,18 +6689,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SI(VIGENTE HASTA EL OCTUBRE 2026)</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Organico NOP</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6972,21 +6709,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Si (vigencia hasta el 01/04/2027) IMO CERT Latinoamerica LTDA , N° de certificado: 6400012046</t>
+          <t>San Martín</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Si (vigente hasta julio del 2028)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Certificación Comercio Justo: FLO ID 33184
-Certificación Ogánica: BIOLATINA
-Certificación Café Practices
-Certificación Rainforest Alliance</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6997,18 +6729,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Si (vigente a noviembre 2026)</t>
+          <t>San Martín</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>En proceso</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Orgánico Nop, Organico para EEUU, Organico para la UE</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -7019,18 +6749,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SI CUENTA</t>
+          <t>Ayacucho</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NO  CUENTA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
+          <t>san martin</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -7041,18 +6769,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SI(VIGENTE HASTA EL 31 DE MARZO 2026)</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SI (VIGENTE HASTA EL 30 DE ABRIL 2026) </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -7063,18 +6789,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SI ( VIGENTE HASTA AGOSTO 2026)</t>
+          <t>Pasco</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SI (VIGENTE HASTA SEPTIEMBRE 2026)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIRD FRIENDLY / LIBRE TRABAJO INFANTIL  </t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -7085,15 +6809,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SI (Vigente hasta 31 de agosto del 2026)</t>
+          <t>Junín</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SI. Vigente </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7103,19 +6829,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Si (vigencia hasta el 23/10/2026) certificación de OCI Internacionla N° LPO -00750</t>
+          <t>San Martín</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Si (vigencia hasta junio del 2028)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Certificación Orgánica
-Certificación Comercio Justo (Fairtrade)</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -7126,18 +6849,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UE (PE-BIO-178.604-0001170.2025.001 vigencia 18/11/2026) USA ( ID NOP  6250042027 vigencia 19/08/2026) JAS (CE-013613-2025  vigencia 14/06/2026)</t>
+          <t>San Martín</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FLO ID 40548  vigencia 13/08/2026</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Rainforest Alliance (RA_00073022201 vigencia 10/03/2026)</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -7148,18 +6869,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2511042 PE, VIGENCIA HASTA 16 NOV 2026</t>
+          <t>Junín</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FLO ID 41859, VIGENCIA HASTA 24 DIC 2029</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>IMO cert, Fairtrade</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -7170,15 +6889,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Cajamarca</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7186,16 +6907,18 @@
           <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Junín</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FLO ID 1931022; VIGENCIA HASTA SETIEMBRE 2028</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Fairtrade</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -7206,18 +6929,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Si (OCIA_2114, VENCIDO en proceso de Renovación)</t>
+          <t>San Martín</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Si (FAIR TRADE USA, VENCE 08/04/2028)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NO TIENE</t>
-        </is>
+          <t>pacMAYOR|san martin</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -7228,19 +6949,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>organico: NOP, COR</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NO CUENTA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ORGANICO NOP, COR
-</t>
-        </is>
+          <t>san martin</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7254,581 +6972,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Organización</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Año de intervención</t>
+          <t>inicio_actividades</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Colocar la Etapa en la que se encuentra el PAC: Formulación Ejecución Finalizado</t>
+          <t>inscripcion_sunat</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Intervención 2020-2026</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Indicar el avance con el reglamento de la EUDR</t>
+          <t>fecha_invertida</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Cooperativa Agraria Valle del Biavo Ltda</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>41626</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>41261</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.75</v>
+          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>42095</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>42094</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.75</v>
+          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>44873</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>44784</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.75</v>
+          <t>Cooperativa Agraria Yuraq Yacu</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>42416</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>42376</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera la Florida</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.75</v>
+          <t>Cooperativa Agria Tropical Products</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>43435</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>43433</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Cafetalera CASIL LTDA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Valle Grande</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+          <t>Cooperativa Agraria Line Coffee Marañon</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>44986</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>44889</v>
+      </c>
+      <c r="D7" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Valle del Biavo Ltda</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Yuraq Yacu</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>No se cuenta con la información debido a que nose tiene aun intervención como Agromercado</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Cafetalera OCUMAL</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>50 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Empadronados PPA 64.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Asociación Agroexportadora de la Región San Martín</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Cooperativa Agria Tropical Products</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Asociación de Productores Cerro Blanco</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cooperativa Agraria Line Coffee Marañon</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="n">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -7842,734 +7104,790 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Organización</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Beneficiarios total 2018</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Beneficiarios total 2019</t>
+          <t>Región</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Beneficiarios total 2020</t>
+          <t>Provincia</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Beneficiarios total 2021</t>
+          <t>Tipo de Contribuyente (SUNAT)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Beneficiarios total 2022</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Beneficiarios total 2023</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Beneficiarios total 2024</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Beneficiarios total 2025</t>
+          <t>CIIU Principal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>20132489824</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Calca</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TRANSPORTE DE CARGA POR CARRETERA.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>20132505455</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>112</v>
-      </c>
-      <c r="I3" t="n">
-        <v>111</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>La Convención</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EXPLOTACION MIXTA.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>20132517119</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>129</v>
-      </c>
-      <c r="I4" t="n">
-        <v>129</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>La Convención</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ELAB. CACAO, CHOCOLATE Y CONFIT.</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>20136201213</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I5" t="n">
-        <v>565</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>La Convención</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VTA. MAY. DE OTROS PRODUCTOS.</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>20140181405</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera la Florida</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Junín</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Chanchamayo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CULTIVO DE FRUTAS.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>20140292657</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>49</v>
-      </c>
-      <c r="I7" t="n">
-        <v>60</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>La Convención</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CULTIVO DE FRUTAS.</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>20147443120</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>La Convención</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VTA. MAY. MATERIALES DE CONSTRUCCION.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>20200880448</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Calca</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VTA. MAY. DE OTROS PRODUCTOS.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>20479595276</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera CASIL LTDA</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>195</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cajamarca</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CULTIVOS DE CEREALES.</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>20542209951</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Valle Grande</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>606</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Martín</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Moyobamba</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VTA. MIN. ALIMENTOS, BEBIDAS, TABACO.</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>20542264544</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Valle del Biavo Ltda</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>22</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>San Martín</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bellavista</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CULTIVOS DE CEREALES.</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>20561140091</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>728</v>
-      </c>
-      <c r="I13" t="n">
-        <v>453</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Utcubamba</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CULTIVOS DE CEREALES.</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>20600263286</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>530</v>
-      </c>
-      <c r="H14" t="n">
-        <v>517</v>
-      </c>
-      <c r="I14" t="n">
-        <v>530</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Martín</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Moyobamba</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ASOCIACION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VTA. MAY. DE MATERIAS PRIMAS AGROPEC.</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>20609846314</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>50</v>
-      </c>
-      <c r="H15" t="n">
-        <v>305</v>
-      </c>
-      <c r="I15" t="n">
-        <v>321</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Martín</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lamas</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CULTIVOS DE CEREALES.</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>20600920597</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Yuraq Yacu</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ayacucho</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>La Mar</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VTA. MAY. ALIMENTOS, BEBIDAS Y TABACO.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>20601558204</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Cafetalera OCUMAL</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>256</v>
-      </c>
-      <c r="I17" t="n">
-        <v>244</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Luya</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>EXPLOTACION MIXTA.</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>20602054480</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>59</v>
-      </c>
-      <c r="G18" t="n">
-        <v>59</v>
-      </c>
-      <c r="H18" t="n">
-        <v>59</v>
-      </c>
-      <c r="I18" t="n">
-        <v>59</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pasco</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Oxapampa</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CULTIVO DE FRUTAS.</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>20602488927</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>120</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Junín</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Satipo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VTA. MAY. DE MATERIAS PRIMAS AGROPEC.</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>20602650643</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Asociación Agroexportadora de la Región San Martín</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>607</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Martín</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Moyobamba</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ASOCIACION</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SERVICIOS AGRICOLAS, GANADERAS.</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>20603820691</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>33</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Martín</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bellavista</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VTA. MAY. DE MATERIAS PRIMAS AGROPEC.</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>20603862369</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Cooperativa Agria Tropical Products</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>203</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Junín</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Chanchamayo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CULTIVOS DE CEREALES.</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" t="n">
+        <v>20604309728</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>305</v>
-      </c>
-      <c r="I23" t="n">
-        <v>305</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cajamarca</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ASOCIACION</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CULTIVOS DE CEREALES.</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="n">
+        <v>20605500430</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>265</v>
-      </c>
-      <c r="I24" t="n">
-        <v>257</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Junín</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Chanchamayo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CULTIVOS DE CEREALES.</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" t="n">
+        <v>20606451122</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Asociación de Productores Cerro Blanco</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>31</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Martín</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Moyobamba</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ASOCIACION</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VTA. MAY. DE MATERIAS PRIMAS AGROPEC.</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" t="n">
+        <v>20610286519</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Cooperativa Agraria Line Coffee Marañon</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Utcubamba</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>COOPERATIVAS, SAIS, CAPS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CULTIVO DE FRUTAS.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8739,6 +8057,2575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Altitud de las unidades productivas: (rango - m.s.n.m)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Número de socios (varones)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Numero de socias (Mujeres)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Numero de hectareas totales de la organización</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Producto Dom</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1400 - 2150 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1500 - 1950 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3" t="n">
+        <v>218</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1400 - 2100 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>133</v>
+      </c>
+      <c r="D4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E4" t="n">
+        <v>469</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1750 - 2200 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>472</v>
+      </c>
+      <c r="D5" t="n">
+        <v>188</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1670</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera la Florida</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mayor a 1200 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>339</v>
+      </c>
+      <c r="D6" t="n">
+        <v>111</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1605.8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1750 - 2200 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>38</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1400 - 2100 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>44</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>150</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1600 - 2200 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>38</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera CASIL LTDA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Café de altura</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>136</v>
+      </c>
+      <c r="D10" t="n">
+        <v>42</v>
+      </c>
+      <c r="E10" t="n">
+        <v>437</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Valle Grande</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>800 - 2000 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>468</v>
+      </c>
+      <c r="D11" t="n">
+        <v>154</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4031</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Valle del Biavo Ltda</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000 - 1500 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>372</v>
+      </c>
+      <c r="D12" t="n">
+        <v>44</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1248</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1200 - 2100 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>278</v>
+      </c>
+      <c r="D13" t="n">
+        <v>73</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1045.6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>800 - 1600 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>607</v>
+      </c>
+      <c r="D14" t="n">
+        <v>190</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2110</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1000 - 1400 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>444</v>
+      </c>
+      <c r="D15" t="n">
+        <v>254</v>
+      </c>
+      <c r="E15" t="n">
+        <v>921.1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Yuraq Yacu</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>750 - 2000 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>75</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CACAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera OCUMAL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1300 - 2200 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>205</v>
+      </c>
+      <c r="D17" t="n">
+        <v>51</v>
+      </c>
+      <c r="E17" t="n">
+        <v>685</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1100 - 1850 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>91</v>
+      </c>
+      <c r="D18" t="n">
+        <v>86</v>
+      </c>
+      <c r="E18" t="n">
+        <v>213</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1200 - 1500 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>103</v>
+      </c>
+      <c r="D19" t="n">
+        <v>59</v>
+      </c>
+      <c r="E19" t="n">
+        <v>454.5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Asociación Agroexportadora de la Región San Martín</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1100 - 1700 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>607</v>
+      </c>
+      <c r="D20" t="n">
+        <v>155</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1000 - 1500 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>291</v>
+      </c>
+      <c r="D21" t="n">
+        <v>90</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cooperativa Agria Tropical Products</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mayor a 1200 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>135</v>
+      </c>
+      <c r="D22" t="n">
+        <v>68</v>
+      </c>
+      <c r="E22" t="n">
+        <v>609</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Café de altura</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>236</v>
+      </c>
+      <c r="D23" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" t="n">
+        <v>699</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mayor a 1200 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>165</v>
+      </c>
+      <c r="D24" t="n">
+        <v>92</v>
+      </c>
+      <c r="E24" t="n">
+        <v>771</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Cerro Blanco</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>800 - 2000 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>141</v>
+      </c>
+      <c r="D25" t="n">
+        <v>46</v>
+      </c>
+      <c r="E25" t="n">
+        <v>600</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CAFÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Line Coffee Marañon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1100 - 2200 m s. n. m.</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>78</v>
+      </c>
+      <c r="D26" t="n">
+        <v>66</v>
+      </c>
+      <c r="E26" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CAFE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Certificación Organica vigente (colocar el numero de certificado y la fecha de la vigencia)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Certificación Comercio Justo (colocar el numero de certificado y la fecha de la vigencia)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Con que otras certificaciones vigentes cuentan (tambien incluir la vigencia de cada uno)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Certificacion Organica, vigencia hasta 14/08/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Vigencia organica hasta 26/03/2027</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Certificacion Organica, 26 de noviembre del 2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Certificación Orgánica, Vigencia  hasta agosto 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fairtrade hasta junio 2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Certificación Orgánica, vigencia hasta agosto 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fair trade hasta junio 2027</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera la Florida</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1780867353, VIGENCIA HASTA 06 FEB 2028</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FLO ID 796, VIGENCIA HASTA 24 DIC 2028</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BIRD FRIENDEY y Fairtrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Certificacion Organica, , vigencia  hasta agosto 2026.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FairTrade (en proceso)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Certificacion Organica, vigencia hasta 14/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Vigencia organica hasta 26/03/2027</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Certificacion Organica, vigencia hasta 14/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vigencia organica hasta 26/03/2027</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera CASIL LTDA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Valle Grande</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Si (CU827371 - Vence 24/08/2026) </t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Si ( FAIR TRADE INTERNACIONAL - 28953 - 27/07/2027), (FAIR TRADING USA - 101034770 - 27/07/2027)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RAIN FOREST ( RA_00079662202, VENCE 24/08/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Valle del Biavo Ltda</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PE-BIO-149.604-0001347.2025.002 VIGENCIA 07/09/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FLO ID: 30733  vigencia (02/02/2028)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rainforest Alliance  RA_00079682202 vigencia(15/07/2027) C831412RA_01_2025
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SI(VIGENTE HASTA EL OCTUBRE 2026)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Organico NOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Si (vigencia hasta el 01/04/2027) IMO CERT Latinoamerica LTDA , N° de certificado: 6400012046</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Si (vigente hasta julio del 2028)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Certificación Comercio Justo: FLO ID 33184
+Certificación Ogánica: BIOLATINA
+Certificación Café Practices
+Certificación Rainforest Alliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Si (vigente a noviembre 2026)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Orgánico Nop, Organico para EEUU, Organico para la UE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Yuraq Yacu</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SI CUENTA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NO  CUENTA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera OCUMAL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SI(VIGENTE HASTA EL 31 DE MARZO 2026)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SI (VIGENTE HASTA EL 30 DE ABRIL 2026) </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SI ( VIGENTE HASTA AGOSTO 2026)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SI (VIGENTE HASTA SEPTIEMBRE 2026)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIRD FRIENDLY / LIBRE TRABAJO INFANTIL  </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SI (Vigente hasta 31 de agosto del 2026)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SI. Vigente </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Asociación Agroexportadora de la Región San Martín</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Si (vigencia hasta el 23/10/2026) certificación de OCI Internacionla N° LPO -00750</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Si (vigencia hasta junio del 2028)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Certificación Orgánica
+Certificación Comercio Justo (Fairtrade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UE (PE-BIO-178.604-0001170.2025.001 vigencia 18/11/2026) USA ( ID NOP  6250042027 vigencia 19/08/2026) JAS (CE-013613-2025  vigencia 14/06/2026)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FLO ID 40548  vigencia 13/08/2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance (RA_00073022201 vigencia 10/03/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cooperativa Agria Tropical Products</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2511042 PE, VIGENCIA HASTA 16 NOV 2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FLO ID 41859, VIGENCIA HASTA 24 DIC 2029</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>IMO cert, Fairtrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FLO ID 1931022; VIGENCIA HASTA SETIEMBRE 2028</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fairtrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Cerro Blanco</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Si (OCIA_2114, VENCIDO en proceso de Renovación)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Si (FAIR TRADE USA, VENCE 08/04/2028)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NO TIENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Line Coffee Marañon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>organico: NOP, COR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NO CUENTA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORGANICO NOP, COR
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Año de intervención</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Colocar la Etapa en la que se encuentra el PAC: Formulación Ejecución Finalizado</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Intervención 2020-2026</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Indicar el avance con el reglamento de la EUDR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera la Florida</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera CASIL LTDA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Valle Grande</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Valle del Biavo Ltda</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Yuraq Yacu</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No se cuenta con la información debido a que nose tiene aun intervención como Agromercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera OCUMAL</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>50 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Empadronados PPA 64.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Asociación Agroexportadora de la Región San Martín</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cooperativa Agria Tropical Products</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Cerro Blanco</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Line Coffee Marañon</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Beneficiarios total 2018</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Beneficiarios total 2019</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Beneficiarios total 2020</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Beneficiarios total 2021</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Beneficiarios total 2022</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Beneficiarios total 2023</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Beneficiarios total 2024</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Beneficiarios total 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Chancamayo Ltda N° 008-B-VII,</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Aguilayoc Ltda. 084</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>112</v>
+      </c>
+      <c r="I3" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Mateo Pumacahua Ltda. 185</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>129</v>
+      </c>
+      <c r="I4" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Central de Cooperativas Agrarias Cafetaleras Cocla Ltda. Nro 281</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I5" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera la Florida</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Ccochapampa Ltda.</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>49</v>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Tirijuay Pavayoc Ltda 13-B-VII</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera Jorge Chavez Ltda</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera CASIL LTDA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Valle Grande</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Valle del Biavo Ltda</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Agroecológica Cafetalera de Lonya Grande</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>728</v>
+      </c>
+      <c r="I13" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Selva Nororiental - APROSELVANOR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>530</v>
+      </c>
+      <c r="H14" t="n">
+        <v>517</v>
+      </c>
+      <c r="I14" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Familias Campesinas Emprendedoras y Resilientes del Perú - CAFCER</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" t="n">
+        <v>305</v>
+      </c>
+      <c r="I15" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Yuraq Yacu</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Cafetalera OCUMAL</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>256</v>
+      </c>
+      <c r="I17" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Ecológica De Mujeres Cafetaleras Villa Rica</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>59</v>
+      </c>
+      <c r="G18" t="n">
+        <v>59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Ecologico Rosas Pampa Ltda - Caeco Rosas Pampa Ltda</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Asociación Agroexportadora de la Región San Martín</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Servicios Múltiples Cordillera Azul</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cooperativa Agria Tropical Products</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Agroecológicos San Juan - APROCASJ</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>305</v>
+      </c>
+      <c r="I23" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria de Productores Ecológicos los Chankas Valle del Río Perené</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>265</v>
+      </c>
+      <c r="I24" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Asociación de Productores Cerro Blanco</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cooperativa Agraria Line Coffee Marañon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -9585,7 +11472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10213,7 +12100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10817,7 +12704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/reports/informe_eudr_tablas.xlsx
+++ b/reports/informe_eudr_tablas.xlsx
@@ -6367,7 +6367,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dispersión geográfica real de los socios — gap ya identificado, pendiente de encuesta</t>
+          <t>Dispersión geográfica real de los socios — brecha ya identificada, pendiente de encuesta</t>
         </is>
       </c>
     </row>
